--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00126_19130805.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.8.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -919,7 +919,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00126_19130805.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00126_19130805.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,11 +431,11 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="51" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
-    <col width="53" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: air is fresh and pure â€” a tonic to</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 8</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -642,7 +646,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L51: line starts with punctuation glued to text :: *nesday.0</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Moderate to fresh northerly to •</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>603</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -688,12 +692,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L427: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” AT-</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN :: â™¦ Toronto, Aug. 5.â€”Maritime: Â°</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -705,15 +709,19 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
-      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • ately warm today and cn Wed-•</t>
+        </is>
+      </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: _________â€¢</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • westerly winds, fair and moder-°</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -759,12 +767,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L493: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: When You Think Shoes â€” Think Campbell's</t>
+          <t>L254: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Moderate to fresh northerly to â€¢</t>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Toronto, Aug. 5.—Maritime: °</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -784,7 +792,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L488: line starts with digit/letter garbage token | suspicious token(s): 1just (letter/digit mix) :: 1just as serviceable for business</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • ately warm today and cn Wed-•</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -802,12 +810,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -824,21 +832,17 @@
           <t>L423: suspicious token(s): LaBelle (odd internal casing) :: derham makes it possible for LaBelle</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ER OIL STOVES, equippÃ©d with</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ westerly winds, fair and moder-Â°</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Moderate to fresh northerly to •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L21: isolated marker/symbol line :: â†’</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -849,7 +853,11 @@
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L51: line starts with punctuation glued to text :: *nesday.0</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -890,7 +898,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ ately warm today and cn Wed-â€¢</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • westerly winds, fair and moder-°</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -908,7 +916,11 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: _________•</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -949,7 +961,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: _________â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • ately warm today and cn Wed-•</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -967,7 +979,11 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L265: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • nell, K. F. Bonnell and Harry McFar-</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1008,7 +1024,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: VI. at St. Dunstanâ€™s school, who is</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: _________•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1026,7 +1042,11 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L488: line starts with digit/letter garbage token | suspicious token(s): 1just (letter/digit mix) :: 1just as serviceable for business</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1067,7 +1087,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L265: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ nell, K. F. Bonnell and Harry McFar-</t>
+          <t>L265: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • nell, K. F. Bonnell and Harry McFar-</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1101,12 +1121,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1124,11 +1144,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L312: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”.e usual contract.</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1165,7 +1181,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1183,11 +1199,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L318: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A ladiesâ€™ swimming race has been :</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1219,12 +1231,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1238,25 +1250,21 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L648: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): VanWarts (odd internal casing) :: VanWartsâ€™</t>
+          <t>L648: suspicious token(s): VanWarts (odd internal casing) :: VanWarts’</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 'Fredericton, and if we donâ€™t tear it</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L525: isolated marker/symbol line :: 80</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: -</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: _________•</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1283,7 +1291,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1301,21 +1309,17 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: air is fresh and pureâ€”a tonic to</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L553: symbol-only separator/garbage line :: $2.40</t>
+          <t>L254: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: !</t>
+          <t>L101: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1356,21 +1360,17 @@
       </c>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L490: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from $2.50 upwardâ€” depending</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L570: isolated marker/symbol line :: 2</t>
+          <t>L525: isolated marker/symbol line :: 80</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L252: isolated marker/symbol line :: /</t>
+          <t>L131: isolated marker/symbol line :: !</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1407,21 +1407,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ATâ€”</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: X</t>
+          <t>L553: symbol-only separator/garbage line :: $2.40</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L260: isolated marker/symbol line :: K</t>
+          <t>L252: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1458,17 +1454,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L648: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): VanWarts (odd internal casing) :: VanWartsâ€™</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="inlineStr"/>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>L570: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L282: isolated marker/symbol line :: 5</t>
+          <t>L260: isolated marker/symbol line :: K</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1505,17 +1501,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At last eveningâ€™s meeting of the</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
-      <c r="N17" s="1" t="inlineStr"/>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>L577: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: I</t>
+          <t>L282: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1540,17 +1536,13 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: When You Think Shoesâ€”Think Campbollâ€™s</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L327: isolated marker/symbol line :: +</t>
+          <t>L326: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1575,17 +1567,13 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L765: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Gagetown ser â€˜ce.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L392: isolated marker/symbol line :: #</t>
+          <t>L327: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1616,7 +1604,7 @@
       <c r="N20" s="1" t="inlineStr"/>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: :</t>
+          <t>L392: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1647,7 +1635,7 @@
       <c r="N21" s="1" t="inlineStr"/>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L403: isolated marker/symbol line :: 1</t>
+          <t>L402: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1678,7 +1666,7 @@
       <c r="N22" s="1" t="inlineStr"/>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L415: isolated marker/symbol line :: o</t>
+          <t>L403: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1709,7 +1697,7 @@
       <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L452: isolated marker/symbol line :: I</t>
+          <t>L415: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1740,7 +1728,7 @@
       <c r="N24" s="1" t="inlineStr"/>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L453: isolated marker/symbol line :: F</t>
+          <t>L452: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1771,7 +1759,7 @@
       <c r="N25" s="1" t="inlineStr"/>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 05</t>
+          <t>L453: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1802,7 +1790,7 @@
       <c r="N26" s="1" t="inlineStr"/>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L498: isolated marker/symbol line :: e</t>
+          <t>L497: isolated marker/symbol line :: 05</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1833,7 +1821,7 @@
       <c r="N27" s="1" t="inlineStr"/>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L543: isolated marker/symbol line :: ?</t>
+          <t>L498: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1864,7 +1852,7 @@
       <c r="N28" s="1" t="inlineStr"/>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L587: isolated marker/symbol line :: U</t>
+          <t>L543: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1895,7 +1883,7 @@
       <c r="N29" s="1" t="inlineStr"/>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L604: isolated marker/symbol line :: U</t>
+          <t>L587: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1926,7 +1914,7 @@
       <c r="N30" s="1" t="inlineStr"/>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: I</t>
+          <t>L604: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1957,7 +1945,7 @@
       <c r="N31" s="1" t="inlineStr"/>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L608: isolated marker/symbol line :: w</t>
+          <t>L606: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1988,7 +1976,7 @@
       <c r="N32" s="1" t="inlineStr"/>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L610: isolated marker/symbol line :: I</t>
+          <t>L608: isolated marker/symbol line :: w</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2019,7 +2007,7 @@
       <c r="N33" s="1" t="inlineStr"/>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L650: symbol-only separator/garbage line :: 77-</t>
+          <t>L610: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2050,7 +2038,7 @@
       <c r="N34" s="1" t="inlineStr"/>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L774: symbol-only separator/garbage line :: $2.40</t>
+          <t>L650: symbol-only separator/garbage line :: 77-</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2081,7 +2069,7 @@
       <c r="N35" s="1" t="inlineStr"/>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L805: isolated marker/symbol line :: 00</t>
+          <t>L774: symbol-only separator/garbage line :: $2.40</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2095,6 +2083,37 @@
       <c r="X35" s="1" t="inlineStr"/>
       <c r="Y35" s="1" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
+      <c r="L36" s="1" t="inlineStr"/>
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L805: isolated marker/symbol line :: 00</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr"/>
+      <c r="V36" s="1" t="inlineStr"/>
+      <c r="W36" s="1" t="inlineStr"/>
+      <c r="X36" s="1" t="inlineStr"/>
+      <c r="Y36" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
